--- a/Design/DAQ port assignments.xlsx
+++ b/Design/DAQ port assignments.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="309">
   <si>
     <t>Model: 6343</t>
   </si>
@@ -955,7 +955,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -994,6 +994,11 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1027,7 +1032,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1050,6 +1055,9 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="16" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1126,11 +1134,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1169950838"/>
-        <c:axId val="938370964"/>
+        <c:axId val="2053215707"/>
+        <c:axId val="1255253683"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1169950838"/>
+        <c:axId val="2053215707"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1194,10 +1202,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="938370964"/>
+        <c:crossAx val="1255253683"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="938370964"/>
+        <c:axId val="1255253683"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1261,7 +1269,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1169950838"/>
+        <c:crossAx val="2053215707"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1337,11 +1345,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="832185496"/>
-        <c:axId val="1843721142"/>
+        <c:axId val="1150092346"/>
+        <c:axId val="904290941"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="832185496"/>
+        <c:axId val="1150092346"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1405,10 +1413,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1843721142"/>
+        <c:crossAx val="904290941"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1843721142"/>
+        <c:axId val="904290941"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1472,7 +1480,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="832185496"/>
+        <c:crossAx val="1150092346"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1548,11 +1556,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1006933306"/>
-        <c:axId val="1773815239"/>
+        <c:axId val="319443227"/>
+        <c:axId val="1132621297"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1006933306"/>
+        <c:axId val="319443227"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1616,10 +1624,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1773815239"/>
+        <c:crossAx val="1132621297"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1773815239"/>
+        <c:axId val="1132621297"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1683,7 +1691,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1006933306"/>
+        <c:crossAx val="319443227"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1759,11 +1767,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="184103431"/>
-        <c:axId val="835337892"/>
+        <c:axId val="917117773"/>
+        <c:axId val="480199094"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="184103431"/>
+        <c:axId val="917117773"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1827,10 +1835,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="835337892"/>
+        <c:crossAx val="480199094"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="835337892"/>
+        <c:axId val="480199094"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1894,7 +1902,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="184103431"/>
+        <c:crossAx val="917117773"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1970,11 +1978,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1300663626"/>
-        <c:axId val="838823324"/>
+        <c:axId val="175106977"/>
+        <c:axId val="2011227935"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1300663626"/>
+        <c:axId val="175106977"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2038,10 +2046,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="838823324"/>
+        <c:crossAx val="2011227935"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="838823324"/>
+        <c:axId val="2011227935"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2105,7 +2113,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1300663626"/>
+        <c:crossAx val="175106977"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -2181,11 +2189,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1338397064"/>
-        <c:axId val="2062071847"/>
+        <c:axId val="1079110820"/>
+        <c:axId val="145405229"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1338397064"/>
+        <c:axId val="1079110820"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2249,10 +2257,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2062071847"/>
+        <c:crossAx val="145405229"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2062071847"/>
+        <c:axId val="145405229"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2316,7 +2324,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1338397064"/>
+        <c:crossAx val="1079110820"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -2392,11 +2400,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="871711196"/>
-        <c:axId val="332573830"/>
+        <c:axId val="1170385592"/>
+        <c:axId val="1686660380"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="871711196"/>
+        <c:axId val="1170385592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2460,10 +2468,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="332573830"/>
+        <c:crossAx val="1686660380"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="332573830"/>
+        <c:axId val="1686660380"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2527,7 +2535,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="871711196"/>
+        <c:crossAx val="1170385592"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -2551,11 +2559,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="754739096"/>
-        <c:axId val="1945132630"/>
+        <c:axId val="638016459"/>
+        <c:axId val="2025807089"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="754739096"/>
+        <c:axId val="638016459"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2619,10 +2627,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1945132630"/>
+        <c:crossAx val="2025807089"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1945132630"/>
+        <c:axId val="2025807089"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2634,7 +2642,7 @@
             <a:noFill/>
           </a:ln>
         </c:spPr>
-        <c:crossAx val="754739096"/>
+        <c:crossAx val="638016459"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -13601,12 +13609,10 @@
       <c r="C4" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>179</v>
-      </c>
+      <c r="D4" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -14141,12 +14147,10 @@
       <c r="C40" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D40" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>206</v>
-      </c>
+      <c r="D40" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="E40" s="7"/>
       <c r="F40" s="7" t="s">
         <v>204</v>
       </c>
@@ -14471,14 +14475,8 @@
       <c r="C60" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D60" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>245</v>
+      <c r="D60" s="6">
+        <v>0.0</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -14488,14 +14486,8 @@
       <c r="C61" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D61" s="1">
-        <v>28.0</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>247</v>
+      <c r="D61" s="6">
+        <v>0.0</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -14508,11 +14500,8 @@
       <c r="C62" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D62" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>251</v>
+      <c r="D62" s="6">
+        <v>0.0</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -15733,8 +15722,8 @@
       <c r="C4" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="7">
-        <v>2.0</v>
+      <c r="D4" s="14">
+        <v>0.0</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>179</v>
@@ -16273,8 +16262,8 @@
       <c r="C40" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D40" s="7">
-        <v>3.0</v>
+      <c r="D40" s="14">
+        <v>0.0</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>206</v>
@@ -16603,8 +16592,8 @@
       <c r="C60" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D60" s="1">
-        <v>24.0</v>
+      <c r="D60" s="6">
+        <v>0.0</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>244</v>
@@ -16620,8 +16609,8 @@
       <c r="C61" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D61" s="1">
-        <v>14.0</v>
+      <c r="D61" s="6">
+        <v>0.0</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>251</v>
@@ -16637,8 +16626,8 @@
       <c r="C62" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D62" s="1">
-        <v>28.0</v>
+      <c r="D62" s="6">
+        <v>0.0</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>244</v>

--- a/Design/DAQ port assignments.xlsx
+++ b/Design/DAQ port assignments.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="325">
   <si>
     <t>Model: 6343</t>
   </si>
@@ -921,31 +921,79 @@
     <t>Monitor Common</t>
   </si>
   <si>
+    <t>A1-00: Language Selection</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>A1-01: Access Level Selection</t>
+  </si>
+  <si>
+    <t>Access is restricted</t>
+  </si>
+  <si>
+    <t>V/f Control - voltage is proportional to frequency</t>
+  </si>
+  <si>
+    <t>A1-03: Initialize Parameters</t>
+  </si>
+  <si>
+    <t>No Initialization</t>
+  </si>
+  <si>
+    <t>Terminals (analog input terminals) using a 0 to 10 Vdc signal to A1 terminal of VFD</t>
+  </si>
+  <si>
+    <t>Ramp to stop, deceleration time set by C1-02</t>
+  </si>
+  <si>
     <t>Reverse operation disabled</t>
   </si>
   <si>
+    <t>C1-01: Acceleration Time 1</t>
+  </si>
+  <si>
+    <t>Time for shaft to accelerate</t>
+  </si>
+  <si>
+    <t>C1-02: Acceleration Time 2</t>
+  </si>
+  <si>
+    <t>Time for shaft to decelerate</t>
+  </si>
+  <si>
+    <t>Time for shaft to decelerate after it is turned off</t>
+  </si>
+  <si>
+    <t>1 or F</t>
+  </si>
+  <si>
+    <t>Not used</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>MB</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>Digital output common</t>
+  </si>
+  <si>
+    <t>H4-02: AM Gain</t>
+  </si>
+  <si>
+    <t>H4-03: AM Bias</t>
+  </si>
+  <si>
+    <t>brwn</t>
+  </si>
+  <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>MB</t>
-  </si>
-  <si>
-    <t>MC</t>
-  </si>
-  <si>
-    <t>Digital output common</t>
-  </si>
-  <si>
-    <t>H4-02: AM Gain</t>
-  </si>
-  <si>
-    <t>H4-03: AM Bias</t>
-  </si>
-  <si>
-    <t>brwn</t>
   </si>
   <si>
     <t>NO, Always detected, Coast to Stop</t>
@@ -1032,7 +1080,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1055,6 +1103,9 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="16" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1134,11 +1185,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="2053215707"/>
-        <c:axId val="1255253683"/>
+        <c:axId val="1361749479"/>
+        <c:axId val="2140791972"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="2053215707"/>
+        <c:axId val="1361749479"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1202,10 +1253,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1255253683"/>
+        <c:crossAx val="2140791972"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1255253683"/>
+        <c:axId val="2140791972"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1269,7 +1320,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2053215707"/>
+        <c:crossAx val="1361749479"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1345,11 +1396,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1150092346"/>
-        <c:axId val="904290941"/>
+        <c:axId val="1133151514"/>
+        <c:axId val="1981817209"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1150092346"/>
+        <c:axId val="1133151514"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1413,10 +1464,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="904290941"/>
+        <c:crossAx val="1981817209"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="904290941"/>
+        <c:axId val="1981817209"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1480,7 +1531,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1150092346"/>
+        <c:crossAx val="1133151514"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1556,11 +1607,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="319443227"/>
-        <c:axId val="1132621297"/>
+        <c:axId val="1507496584"/>
+        <c:axId val="1742813247"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="319443227"/>
+        <c:axId val="1507496584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1624,10 +1675,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1132621297"/>
+        <c:crossAx val="1742813247"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1132621297"/>
+        <c:axId val="1742813247"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1691,7 +1742,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="319443227"/>
+        <c:crossAx val="1507496584"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1767,11 +1818,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="917117773"/>
-        <c:axId val="480199094"/>
+        <c:axId val="896504001"/>
+        <c:axId val="732581597"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="917117773"/>
+        <c:axId val="896504001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1835,10 +1886,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="480199094"/>
+        <c:crossAx val="732581597"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="480199094"/>
+        <c:axId val="732581597"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1902,7 +1953,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="917117773"/>
+        <c:crossAx val="896504001"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1978,11 +2029,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="175106977"/>
-        <c:axId val="2011227935"/>
+        <c:axId val="1240277337"/>
+        <c:axId val="1708947078"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="175106977"/>
+        <c:axId val="1240277337"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2046,10 +2097,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2011227935"/>
+        <c:crossAx val="1708947078"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2011227935"/>
+        <c:axId val="1708947078"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2113,7 +2164,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="175106977"/>
+        <c:crossAx val="1240277337"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -2189,11 +2240,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1079110820"/>
-        <c:axId val="145405229"/>
+        <c:axId val="464299295"/>
+        <c:axId val="917637161"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1079110820"/>
+        <c:axId val="464299295"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2257,10 +2308,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="145405229"/>
+        <c:crossAx val="917637161"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="145405229"/>
+        <c:axId val="917637161"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2324,7 +2375,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1079110820"/>
+        <c:crossAx val="464299295"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -2400,11 +2451,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1170385592"/>
-        <c:axId val="1686660380"/>
+        <c:axId val="1886825471"/>
+        <c:axId val="1507670327"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1170385592"/>
+        <c:axId val="1886825471"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2468,10 +2519,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1686660380"/>
+        <c:crossAx val="1507670327"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1686660380"/>
+        <c:axId val="1507670327"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2535,7 +2586,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1170385592"/>
+        <c:crossAx val="1886825471"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -2559,11 +2610,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="638016459"/>
-        <c:axId val="2025807089"/>
+        <c:axId val="2035485264"/>
+        <c:axId val="1218112142"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="638016459"/>
+        <c:axId val="2035485264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2627,10 +2678,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2025807089"/>
+        <c:crossAx val="1218112142"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2025807089"/>
+        <c:axId val="1218112142"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2642,7 +2693,7 @@
             <a:noFill/>
           </a:ln>
         </c:spPr>
-        <c:crossAx val="638016459"/>
+        <c:crossAx val="2035485264"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -13606,13 +13657,15 @@
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
-      <c r="C4" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D4" s="14">
+      <c r="C4" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="D4" s="6">
         <v>0.0</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="14" t="s">
+        <v>300</v>
+      </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -13638,9 +13691,15 @@
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
+      <c r="C5" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="D5" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>302</v>
+      </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -13666,9 +13725,15 @@
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
+      <c r="C6" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D6" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>303</v>
+      </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -13694,9 +13759,15 @@
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="C7" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>305</v>
+      </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -13890,8 +13961,8 @@
       <c r="D15" s="1">
         <v>1.0</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>182</v>
+      <c r="E15" s="6" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -13912,8 +13983,8 @@
       <c r="D17" s="1">
         <v>0.0</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>186</v>
+      <c r="E17" s="6" t="s">
+        <v>307</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>187</v>
@@ -13927,7 +13998,7 @@
         <v>1.0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -13962,16 +14033,41 @@
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D24" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="C25" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D25" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="C26" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D26" s="1">
         <v>2.0</v>
       </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
+      <c r="E26" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="C27" s="6"/>
+    </row>
     <row r="28" ht="14.25" customHeight="1"/>
     <row r="29" ht="14.25" customHeight="1"/>
     <row r="30" ht="14.25" customHeight="1">
@@ -14004,8 +14100,8 @@
       <c r="C32" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>300</v>
+      <c r="D32" s="15" t="s">
+        <v>314</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
@@ -14147,7 +14243,7 @@
       <c r="C40" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="15">
         <v>0.0</v>
       </c>
       <c r="E40" s="7"/>
@@ -14475,9 +14571,7 @@
       <c r="C60" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D60" s="6">
-        <v>0.0</v>
-      </c>
+      <c r="D60" s="6"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="1" t="s">
@@ -14486,8 +14580,11 @@
       <c r="C61" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D61" s="6">
-        <v>0.0</v>
+      <c r="D61" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -14500,9 +14597,7 @@
       <c r="C62" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D62" s="6">
-        <v>0.0</v>
-      </c>
+      <c r="D62" s="6"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="1" t="s">
@@ -14511,6 +14606,12 @@
       <c r="C63" s="1" t="s">
         <v>253</v>
       </c>
+      <c r="D63" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="1" t="s">
@@ -14518,6 +14619,12 @@
       </c>
       <c r="C64" s="1" t="s">
         <v>255</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
@@ -14563,7 +14670,7 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>266</v>
@@ -14580,7 +14687,7 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>270</v>
@@ -14597,10 +14704,10 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1"/>
@@ -14700,7 +14807,7 @@
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="D82" s="11">
         <v>1.0</v>
@@ -14719,7 +14826,7 @@
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="D83" s="12">
         <v>0.0</v>
@@ -14739,7 +14846,7 @@
         <v>233</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>298</v>
@@ -15722,7 +15829,7 @@
       <c r="C4" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="15">
         <v>0.0</v>
       </c>
       <c r="E4" s="7" t="s">
@@ -16042,7 +16149,7 @@
         <v>1.0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -16120,7 +16227,7 @@
         <v>197</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
@@ -16262,7 +16369,7 @@
       <c r="C40" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="15">
         <v>0.0</v>
       </c>
       <c r="E40" s="7" t="s">
@@ -16599,7 +16706,7 @@
         <v>244</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -16695,7 +16802,7 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>266</v>
@@ -16712,7 +16819,7 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>270</v>
@@ -16729,10 +16836,10 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1"/>
@@ -16832,7 +16939,7 @@
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="D82" s="11">
         <v>1.0</v>
@@ -16851,7 +16958,7 @@
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="D83" s="12">
         <v>0.0</v>
